--- a/resources/inputs.xlsx
+++ b/resources/inputs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romaintilhac/Documents/Research/computing/MATLAB/mixed-source-melting/MSM3_release/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romaintilhac/Documents/Research/resources/GitHub/mixed-source-melting_MSM3/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C832795C-632E-E544-B104-1CF5BC8C34F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC48354-DA86-DB40-BC31-4FF1150EFF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="600" windowWidth="15360" windowHeight="18600" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="600" windowWidth="15360" windowHeight="17420" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ME" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="melting" sheetId="8" r:id="rId6"/>
     <sheet name="CE_Kd" sheetId="9" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
   <si>
     <t>name</t>
   </si>
@@ -190,13 +190,19 @@
   </si>
   <si>
     <t>element</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>default_MC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -225,6 +231,11 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -247,18 +258,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{5AF0D433-CA53-374A-A231-907D9D2AC8B4}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -382,22 +486,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table49" displayName="Table49" ref="A1:E4" totalsRowShown="0">
-  <autoFilter ref="A1:E4" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table49" displayName="Table49" ref="A1:E5" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:E5" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="reference"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="comment"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Se"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Te"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="name" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="reference" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="comment" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Se" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Te" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AB92EBA4-7B7C-934A-B8A9-8B9C4BFC8BE9}" name="Table3" displayName="Table3" ref="A1:D4" totalsRowShown="0">
-  <autoFilter ref="A1:D4" xr:uid="{AB92EBA4-7B7C-934A-B8A9-8B9C4BFC8BE9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AB92EBA4-7B7C-934A-B8A9-8B9C4BFC8BE9}" name="Table3" displayName="Table3" ref="A1:D5" totalsRowShown="0">
+  <autoFilter ref="A1:D5" xr:uid="{AB92EBA4-7B7C-934A-B8A9-8B9C4BFC8BE9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3108977F-17C9-1245-85A5-587DCA26415A}" name="name"/>
     <tableColumn id="2" xr3:uid="{B6E8530E-E833-EA41-990E-981AE1135E32}" name="reference"/>
@@ -1027,68 +1131,86 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D2">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5">
         <v>49</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>3.5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D3">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5">
         <v>84.6</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D4">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
         <v>248</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5">
+        <v>92.52</v>
+      </c>
+      <c r="E5" s="5">
         <v>23</v>
       </c>
     </row>
@@ -1103,7 +1225,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -1158,6 +1280,17 @@
       </c>
       <c r="D4">
         <v>-0.12870000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5">
+        <v>-0.18490000000000001</v>
       </c>
     </row>
   </sheetData>
